--- a/data/proyectos/centroDeProyectos_PMO_2026.xlsx
+++ b/data/proyectos/centroDeProyectos_PMO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Informe_Interactivo/data/proyectos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3583B2E3-90FF-40E7-944E-09B3E132B89F}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42D845F1-3D8F-402A-BDF9-EDE2B85E367C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="511">
   <si>
     <t>Nombre del proyecto</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>5.943.777.982</t>
-  </si>
-  <si>
-    <t>3/01/2022</t>
   </si>
   <si>
     <t>30/11/2026</t>
@@ -191,9 +188,6 @@
   </si>
   <si>
     <t>Gerencia de Talento Humano</t>
-  </si>
-  <si>
-    <t>3/02/2025</t>
   </si>
   <si>
     <t>12/08/2026</t>
@@ -347,9 +341,6 @@
     <t>Gerencia de Tecnologia E Innovacion Digital</t>
   </si>
   <si>
-    <t>22/10/2025</t>
-  </si>
-  <si>
     <t>31/12/2026</t>
   </si>
   <si>
@@ -391,9 +382,6 @@
   </si>
   <si>
     <t>Gerencia de Planeación y Gestión institucional</t>
-  </si>
-  <si>
-    <t>1/04/2025</t>
   </si>
   <si>
     <t>17/04/2026</t>
@@ -451,9 +439,6 @@
     <t>Gerencia de Matriculas</t>
   </si>
   <si>
-    <t>29/09/2025</t>
-  </si>
-  <si>
     <t>20/04/2026</t>
   </si>
   <si>
@@ -499,9 +484,6 @@
   </si>
   <si>
     <t>100.600.000.246</t>
-  </si>
-  <si>
-    <t>28/01/2026</t>
   </si>
   <si>
     <t>26/05/2026</t>
@@ -551,9 +533,6 @@
     <t>12/08/2025</t>
   </si>
   <si>
-    <t>1/05/2025</t>
-  </si>
-  <si>
     <t>8/04/2026</t>
   </si>
   <si>
@@ -653,9 +632,6 @@
   </si>
   <si>
     <t>Dirección de infraestructura</t>
-  </si>
-  <si>
-    <t>1/09/2025</t>
   </si>
   <si>
     <t>30/10/2026</t>
@@ -743,9 +719,6 @@
   </si>
   <si>
     <t>11/09/2023</t>
-  </si>
-  <si>
-    <t>21/04/2023</t>
   </si>
   <si>
     <t>3/01/2025</t>
@@ -776,9 +749,6 @@
     <t>24/01/2025</t>
   </si>
   <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
     <t>15/12/2025</t>
   </si>
   <si>
@@ -800,9 +770,6 @@
     <t>Acreditación Institucional Sede Bogotá-Fase I</t>
   </si>
   <si>
-    <t>2/06/2022</t>
-  </si>
-  <si>
     <t>26/01/2023</t>
   </si>
   <si>
@@ -837,9 +804,6 @@
   </si>
   <si>
     <t>86.300.774</t>
-  </si>
-  <si>
-    <t>13/01/2025</t>
   </si>
   <si>
     <t>17/12/2025</t>
@@ -879,9 +843,6 @@
     <t>6/05/2024</t>
   </si>
   <si>
-    <t>16/05/2022</t>
-  </si>
-  <si>
     <t>10/01/2024</t>
   </si>
   <si>
@@ -916,9 +877,6 @@
   </si>
   <si>
     <t>100.600.000.213</t>
-  </si>
-  <si>
-    <t>3/06/2024</t>
   </si>
   <si>
     <t>31/01/2025</t>
@@ -963,9 +921,6 @@
     <t>22.325.855</t>
   </si>
   <si>
-    <t>2/03/2022</t>
-  </si>
-  <si>
     <t>13/12/2023</t>
   </si>
   <si>
@@ -1000,9 +955,6 @@
   </si>
   <si>
     <t>70.805.747</t>
-  </si>
-  <si>
-    <t>17/03/2023</t>
   </si>
   <si>
     <t>31/12/2024</t>
@@ -1032,9 +984,6 @@
   </si>
   <si>
     <t>Facultad Sociedad Cultura y Creatividad</t>
-  </si>
-  <si>
-    <t>19/10/2023</t>
   </si>
   <si>
     <t>4/12/2024</t>
@@ -1076,9 +1025,6 @@
     <t>31/07/2023</t>
   </si>
   <si>
-    <t>1/02/2023</t>
-  </si>
-  <si>
     <t>18/07/2024</t>
   </si>
   <si>
@@ -1111,9 +1057,6 @@
     <t>10.753.132</t>
   </si>
   <si>
-    <t>1/02/2024</t>
-  </si>
-  <si>
     <t>1/10/2025</t>
   </si>
   <si>
@@ -1139,9 +1082,6 @@
     <t>3.000.000</t>
   </si>
   <si>
-    <t>5/07/2022</t>
-  </si>
-  <si>
     <t>12/03/2024</t>
   </si>
   <si>
@@ -1167,9 +1107,6 @@
     <t>Gerencia de Operaciones</t>
   </si>
   <si>
-    <t>3/06/2022</t>
-  </si>
-  <si>
     <t>14/02/2023</t>
   </si>
   <si>
@@ -1195,9 +1132,6 @@
   </si>
   <si>
     <t>166.256.208</t>
-  </si>
-  <si>
-    <t>1/01/2023</t>
   </si>
   <si>
     <t>2/07/2024</t>
@@ -1232,9 +1166,6 @@
     <t>105.726.210</t>
   </si>
   <si>
-    <t>5/12/2023</t>
-  </si>
-  <si>
     <t>14/06/2024</t>
   </si>
   <si>
@@ -1270,9 +1201,6 @@
     <t>24.985.000</t>
   </si>
   <si>
-    <t>2/01/2023</t>
-  </si>
-  <si>
     <t>23/12/2024</t>
   </si>
   <si>
@@ -1297,9 +1225,6 @@
   </si>
   <si>
     <t>Gerencia de Servicio</t>
-  </si>
-  <si>
-    <t>20/05/2024</t>
   </si>
   <si>
     <t>26/11/2024</t>
@@ -1365,9 +1290,6 @@
     <t>Dirección de servicios Administrativos</t>
   </si>
   <si>
-    <t>16/11/2023</t>
-  </si>
-  <si>
     <t>14/05/2025</t>
   </si>
   <si>
@@ -1396,9 +1318,6 @@
   </si>
   <si>
     <t>1.719.376.386</t>
-  </si>
-  <si>
-    <t>31/01/2023</t>
   </si>
   <si>
     <t>14/02/2024</t>
@@ -1428,9 +1347,6 @@
     <t>20.500.000</t>
   </si>
   <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
     <t>27/12/2023</t>
   </si>
   <si>
@@ -1464,9 +1380,6 @@
     <t>120.232.276</t>
   </si>
   <si>
-    <t>2/11/2021</t>
-  </si>
-  <si>
     <t>17/07/2023</t>
   </si>
   <si>
@@ -1504,9 +1417,6 @@
   </si>
   <si>
     <t>100.600.000.189</t>
-  </si>
-  <si>
-    <t>20/02/2023</t>
   </si>
   <si>
     <t>11/07/2024</t>
@@ -1536,9 +1446,6 @@
     <t>Lucia Solano Felizzola</t>
   </si>
   <si>
-    <t>27/12/2021</t>
-  </si>
-  <si>
     <t>29/07/2022</t>
   </si>
   <si>
@@ -1562,9 +1469,6 @@
   </si>
   <si>
     <t>Facultad Registro y Control</t>
-  </si>
-  <si>
-    <t>7/02/2022</t>
   </si>
   <si>
     <t>10/02/2023</t>
@@ -1595,9 +1499,6 @@
     <t>Gerencia de Servicio y Permanencia</t>
   </si>
   <si>
-    <t>15/01/2024</t>
-  </si>
-  <si>
     <t>30/09/2025</t>
   </si>
   <si>
@@ -1622,9 +1523,6 @@
   </si>
   <si>
     <t>124.000.000</t>
-  </si>
-  <si>
-    <t>1/04/2024</t>
   </si>
   <si>
     <t>30/10/2024</t>
@@ -1685,9 +1583,6 @@
     <t>1.006.000.226</t>
   </si>
   <si>
-    <t>15/11/2024</t>
-  </si>
-  <si>
     <t>7/11/2025</t>
   </si>
   <si>
@@ -1746,9 +1641,6 @@
   </si>
   <si>
     <t>1.006.000.230</t>
-  </si>
-  <si>
-    <t>2/12/2024</t>
   </si>
   <si>
     <t>31/10/2025</t>
@@ -1986,6 +1878,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2009,7 +1902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2022,12 +1915,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2060,14 +1957,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:Y54" totalsRowShown="0">
-  <autoFilter ref="A1:Y54" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nombre del proyecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="0. Estado del proyecto"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ILUMNO"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="% completado"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="% Esperado centro de proyectos"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ind. cumplimiento PWA" dataDxfId="0" dataCellStyle="Porcentaje">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ind. cumplimiento PWA" dataDxfId="1" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>+D2/E2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Propietario"/>
@@ -2082,7 +1978,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="6.2. Presupuesto CAPEX ejecutado"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="6. Orden inversión CAPEX"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="7. Fecha de seguimiento"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Comienzo"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Comienzo" dataDxfId="0"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fin"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Avance"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Siguientes Tareas"/>
@@ -2491,7 +2387,7 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
@@ -2557,107 +2453,107 @@
       <c r="N2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="6">
+        <v>44564</v>
+      </c>
+      <c r="T2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" t="s">
+      <c r="X2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
         <v>41</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>0.94117647058823539</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
         <v>46</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>47</v>
       </c>
-      <c r="K3" t="s">
+      <c r="S3" s="6">
+        <v>45691</v>
+      </c>
+      <c r="T3" t="s">
         <v>48</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="X3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>0.97872340425531923</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
@@ -2666,58 +2562,58 @@
         <v>33</v>
       </c>
       <c r="K4" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="6">
+        <v>45691</v>
+      </c>
+      <c r="T4" t="s">
+        <v>61</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S4" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="V4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="X4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="Y4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>0.96666666666666667</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -2726,304 +2622,304 @@
         <v>33</v>
       </c>
       <c r="K5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" s="6">
+        <v>45964</v>
+      </c>
+      <c r="T5" t="s">
         <v>75</v>
       </c>
-      <c r="S5" t="s">
+      <c r="U5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>77</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="W5" t="s">
         <v>78</v>
       </c>
-      <c r="V5" t="s">
+      <c r="X5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
         <v>86</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>87</v>
       </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="S6" s="6">
+        <v>45952</v>
+      </c>
+      <c r="T6" t="s">
         <v>88</v>
       </c>
-      <c r="K6" t="s">
+      <c r="U6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="S6" t="s">
+      <c r="V6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="T6" t="s">
+      <c r="W6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="X6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="Y6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="Z6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
       <c r="G7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
+        <v>99</v>
+      </c>
+      <c r="S7" s="6">
+        <v>45748</v>
+      </c>
+      <c r="T7" t="s">
         <v>100</v>
       </c>
-      <c r="H7" t="s">
+      <c r="U7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="V7" t="s">
         <v>102</v>
       </c>
-      <c r="S7" t="s">
+      <c r="W7" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T7" t="s">
+      <c r="X7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="Y7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="V7" t="s">
+      <c r="Z7" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>0.93055555555555569</v>
       </c>
       <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>112</v>
+      </c>
+      <c r="I8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" t="s">
         <v>115</v>
       </c>
-      <c r="H8" t="s">
+      <c r="S8" s="6">
+        <v>45929</v>
+      </c>
+      <c r="T8" t="s">
         <v>116</v>
       </c>
-      <c r="I8" t="s">
+      <c r="U8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J8" t="s">
+      <c r="V8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K8" t="s">
+      <c r="W8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="S8" t="s">
+      <c r="X8" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="T8" t="s">
+      <c r="Y8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="Z8" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>0.95454545454545447</v>
       </c>
       <c r="G9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O9" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S9" s="6">
+        <v>46050</v>
+      </c>
+      <c r="T9" t="s">
+        <v>130</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J9" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="V9" t="s">
         <v>132</v>
       </c>
-      <c r="O9" t="s">
+      <c r="W9" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="X9" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="S9" t="s">
+      <c r="Y9" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="T9" t="s">
+      <c r="Z9" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="V9" t="s">
-        <v>138</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="0"/>
         <v>0.95454545454545447</v>
       </c>
       <c r="G10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I10" t="s">
         <v>32</v>
@@ -3032,61 +2928,61 @@
         <v>33</v>
       </c>
       <c r="K10" t="s">
+        <v>141</v>
+      </c>
+      <c r="R10" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="6">
+        <v>45778</v>
+      </c>
+      <c r="T10" t="s">
+        <v>143</v>
+      </c>
+      <c r="U10" t="s">
+        <v>144</v>
+      </c>
+      <c r="V10" t="s">
+        <v>145</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="X10" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="R10" t="s">
+      <c r="Y10" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="S10" t="s">
+      <c r="Z10" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="T10" t="s">
-        <v>150</v>
-      </c>
-      <c r="U10" t="s">
-        <v>151</v>
-      </c>
-      <c r="V10" t="s">
-        <v>152</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z10" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="0"/>
         <v>0.94</v>
       </c>
       <c r="G11" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
@@ -3095,190 +2991,190 @@
         <v>33</v>
       </c>
       <c r="K11" t="s">
+        <v>153</v>
+      </c>
+      <c r="O11" t="s">
+        <v>154</v>
+      </c>
+      <c r="P11" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>156</v>
+      </c>
+      <c r="R11" t="s">
+        <v>157</v>
+      </c>
+      <c r="S11" s="6">
+        <v>45551</v>
+      </c>
+      <c r="T11" t="s">
+        <v>159</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="O11" t="s">
+      <c r="V11" t="s">
         <v>161</v>
       </c>
-      <c r="P11" t="s">
+      <c r="W11" t="s">
         <v>162</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="X11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="R11" t="s">
+      <c r="Y11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="S11" t="s">
+      <c r="Z11" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="T11" t="s">
-        <v>166</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="V11" t="s">
-        <v>168</v>
-      </c>
-      <c r="W11" t="s">
-        <v>169</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="Z11" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E12" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="0"/>
         <v>0.984375</v>
       </c>
       <c r="G12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K12" t="s">
+        <v>173</v>
+      </c>
+      <c r="S12" s="6">
+        <v>45901</v>
+      </c>
+      <c r="T12" t="s">
+        <v>174</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H12" t="s">
+      <c r="W12" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I12" t="s">
+      <c r="X12" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="J12" t="s">
+      <c r="Y12" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="K12" t="s">
+      <c r="Z12" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="S12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T12" t="s">
-        <v>182</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z12" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="0"/>
         <v>0.90909090909090906</v>
       </c>
       <c r="G13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" t="s">
+        <v>184</v>
+      </c>
+      <c r="S13" s="6">
+        <v>45691</v>
+      </c>
+      <c r="T13" t="s">
+        <v>185</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z13" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="H13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" t="s">
-        <v>192</v>
-      </c>
-      <c r="S13" t="s">
-        <v>49</v>
-      </c>
-      <c r="T13" t="s">
-        <v>193</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
         <v>32</v>
@@ -3287,52 +3183,52 @@
         <v>33</v>
       </c>
       <c r="K14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="R14" t="s">
-        <v>204</v>
-      </c>
-      <c r="S14" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="S14" s="6">
+        <v>45037</v>
       </c>
       <c r="T14" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
         <v>32</v>
@@ -3341,52 +3237,52 @@
         <v>33</v>
       </c>
       <c r="K15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="R15" t="s">
-        <v>212</v>
-      </c>
-      <c r="S15" t="s">
-        <v>213</v>
+        <v>203</v>
+      </c>
+      <c r="S15" s="6">
+        <v>45643</v>
       </c>
       <c r="T15" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
@@ -3395,109 +3291,109 @@
         <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>203</v>
-      </c>
-      <c r="S16" t="s">
-        <v>219</v>
+        <v>195</v>
+      </c>
+      <c r="S16" s="6">
+        <v>44714</v>
       </c>
       <c r="T16" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="H17" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
         <v>46</v>
       </c>
-      <c r="J17" t="s">
-        <v>47</v>
-      </c>
       <c r="K17" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="L17" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="M17" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="N17" t="s">
-        <v>230</v>
-      </c>
-      <c r="S17" t="s">
-        <v>231</v>
+        <v>219</v>
+      </c>
+      <c r="S17" s="6">
+        <v>45670</v>
       </c>
       <c r="T17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="H18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I18" t="s">
         <v>32</v>
@@ -3506,190 +3402,190 @@
         <v>33</v>
       </c>
       <c r="K18" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="L18" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="M18" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="R18" t="s">
-        <v>242</v>
-      </c>
-      <c r="S18" t="s">
-        <v>243</v>
+        <v>230</v>
+      </c>
+      <c r="S18" s="6">
+        <v>44697</v>
       </c>
       <c r="T18" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I19" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J19" t="s">
         <v>33</v>
       </c>
       <c r="K19" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="Q19" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="R19" t="s">
-        <v>165</v>
-      </c>
-      <c r="S19" t="s">
-        <v>255</v>
+        <v>158</v>
+      </c>
+      <c r="S19" s="6">
+        <v>45446</v>
       </c>
       <c r="T19" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F20" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="H20" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="I20" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K20" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="L20" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="M20" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="N20" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="R20" t="s">
-        <v>242</v>
-      </c>
-      <c r="S20" t="s">
-        <v>268</v>
+        <v>230</v>
+      </c>
+      <c r="S20" s="6">
+        <v>44622</v>
       </c>
       <c r="T20" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
         <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I21" t="s">
         <v>32</v>
@@ -3698,61 +3594,61 @@
         <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="L21" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="M21" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="N21" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="R21" t="s">
-        <v>242</v>
-      </c>
-      <c r="S21" t="s">
-        <v>279</v>
+        <v>230</v>
+      </c>
+      <c r="S21" s="6">
+        <v>45002</v>
       </c>
       <c r="T21" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
         <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F22" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I22" t="s">
         <v>32</v>
@@ -3761,400 +3657,400 @@
         <v>33</v>
       </c>
       <c r="K22" t="s">
-        <v>286</v>
-      </c>
-      <c r="S22" t="s">
-        <v>287</v>
+        <v>270</v>
+      </c>
+      <c r="S22" s="6">
+        <v>45218</v>
       </c>
       <c r="T22" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="H23" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
+        <v>277</v>
+      </c>
+      <c r="K23" t="s">
         <v>87</v>
       </c>
-      <c r="I23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" t="s">
-        <v>294</v>
-      </c>
-      <c r="K23" t="s">
-        <v>89</v>
-      </c>
       <c r="O23" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="Q23" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="R23" t="s">
-        <v>297</v>
-      </c>
-      <c r="S23" t="s">
-        <v>298</v>
+        <v>280</v>
+      </c>
+      <c r="S23" s="6">
+        <v>44958</v>
       </c>
       <c r="T23" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I24" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="J24" t="s">
         <v>33</v>
       </c>
       <c r="K24" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="L24" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="N24" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="R24" t="s">
-        <v>242</v>
-      </c>
-      <c r="S24" t="s">
-        <v>307</v>
+        <v>230</v>
+      </c>
+      <c r="S24" s="6">
+        <v>45323</v>
       </c>
       <c r="T24" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="J25" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="R25" t="s">
+        <v>280</v>
+      </c>
+      <c r="S25" s="6">
+        <v>44747</v>
+      </c>
+      <c r="T25" t="s">
+        <v>296</v>
+      </c>
+      <c r="X25" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="S25" t="s">
-        <v>315</v>
-      </c>
-      <c r="T25" t="s">
-        <v>316</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="Y25" s="4" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C26" t="s">
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s">
-        <v>322</v>
-      </c>
-      <c r="S26" t="s">
-        <v>323</v>
+        <v>302</v>
+      </c>
+      <c r="S26" s="6">
+        <v>44715</v>
       </c>
       <c r="T26" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
         <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K27" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="M27" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="N27" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="R27" t="s">
-        <v>297</v>
-      </c>
-      <c r="S27" t="s">
-        <v>332</v>
+        <v>280</v>
+      </c>
+      <c r="S27" s="6">
+        <v>44927</v>
       </c>
       <c r="T27" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F28" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="L28" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="M28" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="N28" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="R28" t="s">
-        <v>242</v>
-      </c>
-      <c r="S28" t="s">
-        <v>342</v>
+        <v>230</v>
+      </c>
+      <c r="S28" s="6">
+        <v>45265</v>
       </c>
       <c r="T28" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I29" t="s">
         <v>32</v>
@@ -4163,106 +4059,106 @@
         <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="L29" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="M29" t="s">
-        <v>351</v>
-      </c>
-      <c r="S29" t="s">
-        <v>352</v>
+        <v>328</v>
+      </c>
+      <c r="S29" s="6">
+        <v>44928</v>
       </c>
       <c r="T29" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s">
-        <v>359</v>
-      </c>
-      <c r="S30" t="s">
-        <v>360</v>
+        <v>335</v>
+      </c>
+      <c r="S30" s="6">
+        <v>45432</v>
       </c>
       <c r="T30" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="X30" s="4" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I31" t="s">
         <v>32</v>
@@ -4271,684 +4167,684 @@
         <v>33</v>
       </c>
       <c r="K31" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="N31" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="R31" t="s">
-        <v>242</v>
-      </c>
-      <c r="S31" t="s">
-        <v>352</v>
+        <v>230</v>
+      </c>
+      <c r="S31" s="6">
+        <v>44928</v>
       </c>
       <c r="T31" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="X31" s="4" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C32" t="s">
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>376</v>
-      </c>
-      <c r="S32" t="s">
-        <v>377</v>
+        <v>351</v>
+      </c>
+      <c r="S32" s="6">
+        <v>45246</v>
       </c>
       <c r="T32" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="Z32" s="4" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="H33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
+        <v>86</v>
+      </c>
+      <c r="K33" t="s">
         <v>87</v>
       </c>
-      <c r="I33" t="s">
-        <v>46</v>
-      </c>
-      <c r="J33" t="s">
-        <v>88</v>
-      </c>
-      <c r="K33" t="s">
-        <v>89</v>
-      </c>
       <c r="L33" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="O33" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="P33" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="R33" t="s">
-        <v>242</v>
-      </c>
-      <c r="S33" t="s">
-        <v>387</v>
+        <v>230</v>
+      </c>
+      <c r="S33" s="6">
+        <v>44957</v>
       </c>
       <c r="T33" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="Z33" s="4" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" ref="F34:F65" si="1">+D34/E34</f>
+        <f t="shared" ref="F34:F54" si="1">+D34/E34</f>
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="I34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" t="s">
         <v>46</v>
       </c>
-      <c r="J34" t="s">
-        <v>47</v>
-      </c>
       <c r="K34" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="L34" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="M34" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="R34" t="s">
-        <v>242</v>
-      </c>
-      <c r="S34" t="s">
-        <v>395</v>
+        <v>230</v>
+      </c>
+      <c r="S34" s="6">
+        <v>44936</v>
       </c>
       <c r="T34" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="Y34" s="4" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="Z34" s="4" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="H35" t="s">
         <v>31</v>
       </c>
       <c r="I35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" t="s">
         <v>46</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>47</v>
       </c>
-      <c r="K35" t="s">
-        <v>48</v>
-      </c>
       <c r="L35" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="M35" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="N35" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="R35" t="s">
-        <v>242</v>
-      </c>
-      <c r="S35" t="s">
-        <v>405</v>
+        <v>230</v>
+      </c>
+      <c r="S35" s="6">
+        <v>44502</v>
       </c>
       <c r="T35" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="Z35" s="4" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J36" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K36" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="L36" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="M36" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="N36" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="O36" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="Q36" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="R36" t="s">
-        <v>242</v>
-      </c>
-      <c r="S36" t="s">
-        <v>417</v>
+        <v>230</v>
+      </c>
+      <c r="S36" s="6">
+        <v>44977</v>
       </c>
       <c r="T36" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="Y36" s="4" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="Z36" s="4" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="H37" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="I37" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K37" t="s">
-        <v>132</v>
-      </c>
-      <c r="S37" t="s">
-        <v>425</v>
+        <v>127</v>
+      </c>
+      <c r="S37" s="6">
+        <v>44557</v>
       </c>
       <c r="T37" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="Y37" s="4" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="Z37" s="4" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C38" t="s">
         <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E38" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="H38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s">
-        <v>432</v>
-      </c>
-      <c r="S38" t="s">
-        <v>433</v>
+        <v>401</v>
+      </c>
+      <c r="S38" s="6">
+        <v>44599</v>
       </c>
       <c r="T38" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="Y38" s="4" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="Z38" s="4" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C39" t="s">
         <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="H39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s">
-        <v>440</v>
-      </c>
-      <c r="S39" t="s">
-        <v>441</v>
+        <v>408</v>
+      </c>
+      <c r="S39" s="6">
+        <v>45306</v>
       </c>
       <c r="T39" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="Y39" s="4" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="Z39" s="4" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="H40" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="I40" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J40" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K40" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M40" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="N40" t="s">
-        <v>447</v>
-      </c>
-      <c r="S40" t="s">
-        <v>448</v>
+        <v>414</v>
+      </c>
+      <c r="S40" s="6">
+        <v>45383</v>
       </c>
       <c r="T40" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="Y40" s="4" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="Z40" s="4" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E41" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G41" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" t="s">
         <v>86</v>
       </c>
-      <c r="H41" t="s">
+      <c r="K41" t="s">
         <v>87</v>
       </c>
-      <c r="I41" t="s">
-        <v>46</v>
-      </c>
-      <c r="J41" t="s">
-        <v>88</v>
-      </c>
-      <c r="K41" t="s">
-        <v>89</v>
-      </c>
       <c r="O41" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="P41" t="s">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="Q41" t="s">
-        <v>456</v>
-      </c>
-      <c r="S41" t="s">
-        <v>231</v>
+        <v>422</v>
+      </c>
+      <c r="S41" s="6">
+        <v>45670</v>
       </c>
       <c r="T41" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="X41" s="4" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
       <c r="Y41" s="4" t="s">
-        <v>459</v>
+        <v>425</v>
       </c>
       <c r="Z41" s="4" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s">
         <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" t="s">
         <v>87</v>
       </c>
-      <c r="I42" t="s">
-        <v>46</v>
-      </c>
-      <c r="J42" t="s">
-        <v>294</v>
-      </c>
-      <c r="K42" t="s">
-        <v>89</v>
-      </c>
       <c r="O42" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="P42" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="Q42" t="s">
-        <v>464</v>
-      </c>
-      <c r="S42" t="s">
-        <v>465</v>
+        <v>430</v>
+      </c>
+      <c r="S42" s="6">
+        <v>45611</v>
       </c>
       <c r="T42" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="Z42" s="4" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E43" t="s">
         <v>29</v>
@@ -4958,10 +4854,10 @@
         <v>1.0101010101010102</v>
       </c>
       <c r="G43" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="H43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I43" t="s">
         <v>32</v>
@@ -4970,613 +4866,613 @@
         <v>33</v>
       </c>
       <c r="K43" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="L43" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="M43" t="s">
-        <v>474</v>
-      </c>
-      <c r="S43" t="s">
-        <v>287</v>
+        <v>439</v>
+      </c>
+      <c r="S43" s="6">
+        <v>45218</v>
       </c>
       <c r="T43" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="X43" s="4" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J44" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K44" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="O44" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="P44" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="Q44" t="s">
-        <v>482</v>
-      </c>
-      <c r="S44" t="s">
-        <v>483</v>
+        <v>447</v>
+      </c>
+      <c r="S44" s="6">
+        <v>45628</v>
       </c>
       <c r="T44" t="s">
-        <v>484</v>
+        <v>448</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>486</v>
+        <v>450</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>487</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>488</v>
+        <v>452</v>
       </c>
       <c r="B45" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E45" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F45" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" t="s">
-        <v>491</v>
+        <v>455</v>
       </c>
       <c r="H45" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="I45" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" t="s">
         <v>46</v>
       </c>
-      <c r="J45" t="s">
-        <v>47</v>
-      </c>
       <c r="K45" t="s">
-        <v>227</v>
-      </c>
-      <c r="S45" t="s">
-        <v>76</v>
+        <v>216</v>
+      </c>
+      <c r="S45" s="6">
+        <v>45964</v>
       </c>
       <c r="T45" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="X45" s="4"/>
       <c r="Y45" s="4" t="s">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>494</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="B46" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E46" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F46" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K46" t="s">
-        <v>192</v>
-      </c>
-      <c r="S46" t="s">
-        <v>496</v>
+        <v>184</v>
+      </c>
+      <c r="S46" s="6">
+        <v>46023</v>
       </c>
       <c r="T46" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>497</v>
+        <v>461</v>
       </c>
       <c r="X46" s="4"/>
       <c r="Y46" s="4" t="s">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>499</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>500</v>
+        <v>464</v>
       </c>
       <c r="B47" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C47" t="s">
         <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E47" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F47" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G47" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H47" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J47" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K47" t="s">
-        <v>192</v>
-      </c>
-      <c r="S47" t="s">
-        <v>496</v>
+        <v>184</v>
+      </c>
+      <c r="S47" s="6">
+        <v>46023</v>
       </c>
       <c r="T47" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
       <c r="X47" s="4"/>
       <c r="Y47" s="4" t="s">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>503</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E48" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F48" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G48" t="s">
-        <v>505</v>
+        <v>469</v>
       </c>
       <c r="H48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J48" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s">
-        <v>440</v>
-      </c>
-      <c r="S48" t="s">
-        <v>506</v>
+        <v>408</v>
+      </c>
+      <c r="S48" s="6">
+        <v>46097</v>
       </c>
       <c r="T48" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>507</v>
+        <v>471</v>
       </c>
       <c r="X48" s="4"/>
       <c r="Y48" s="4" t="s">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="Z48" s="4" t="s">
-        <v>509</v>
+        <v>473</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>510</v>
+        <v>474</v>
       </c>
       <c r="B49" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E49" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F49" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G49" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H49" t="s">
-        <v>511</v>
+        <v>475</v>
       </c>
       <c r="I49" t="s">
         <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K49" t="s">
-        <v>238</v>
-      </c>
-      <c r="S49" t="s">
-        <v>512</v>
+        <v>226</v>
+      </c>
+      <c r="S49" s="6">
+        <v>45924</v>
       </c>
       <c r="T49" t="s">
-        <v>512</v>
+        <v>476</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>513</v>
+        <v>477</v>
       </c>
       <c r="X49" s="4"/>
       <c r="Y49" s="4" t="s">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="Z49" s="4" t="s">
-        <v>515</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E50" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F50" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G50" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="H50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J50" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s">
-        <v>440</v>
-      </c>
-      <c r="S50" t="s">
-        <v>517</v>
+        <v>408</v>
+      </c>
+      <c r="S50" s="6">
+        <v>46055</v>
       </c>
       <c r="T50" t="s">
-        <v>517</v>
+        <v>481</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>518</v>
+        <v>482</v>
       </c>
       <c r="X50" s="4"/>
       <c r="Y50" s="4" t="s">
-        <v>519</v>
+        <v>483</v>
       </c>
       <c r="Z50" s="4" t="s">
-        <v>520</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E51" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F51" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G51" t="s">
-        <v>505</v>
+        <v>469</v>
       </c>
       <c r="H51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J51" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K51" t="s">
-        <v>440</v>
-      </c>
-      <c r="S51" t="s">
-        <v>517</v>
+        <v>408</v>
+      </c>
+      <c r="S51" s="6">
+        <v>46055</v>
       </c>
       <c r="T51" t="s">
-        <v>517</v>
+        <v>481</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="X51" s="4" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="Y51" s="4" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
       <c r="Z51" s="4" t="s">
-        <v>525</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="B52" t="s">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="C52" t="s">
         <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E52" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F52" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G52" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I52" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="J52" t="s">
         <v>33</v>
       </c>
       <c r="K52" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="R52" t="s">
-        <v>530</v>
-      </c>
-      <c r="S52" t="s">
-        <v>307</v>
+        <v>494</v>
+      </c>
+      <c r="S52" s="6">
+        <v>45323</v>
       </c>
       <c r="T52" t="s">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>532</v>
+        <v>496</v>
       </c>
       <c r="X52" s="4"/>
       <c r="Y52" s="4" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>534</v>
+        <v>498</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>535</v>
+        <v>499</v>
       </c>
       <c r="B53" t="s">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="C53" t="s">
         <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E53" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F53" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G53" t="s">
-        <v>536</v>
+        <v>500</v>
       </c>
       <c r="H53" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="I53" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="J53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
-        <v>227</v>
-      </c>
-      <c r="S53" t="s">
-        <v>387</v>
+        <v>216</v>
+      </c>
+      <c r="S53" s="6">
+        <v>44957</v>
       </c>
       <c r="T53" t="s">
-        <v>537</v>
+        <v>501</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>538</v>
+        <v>502</v>
       </c>
       <c r="X53" s="4"/>
       <c r="Y53" s="4" t="s">
-        <v>539</v>
+        <v>503</v>
       </c>
       <c r="Z53" s="4" t="s">
-        <v>540</v>
+        <v>504</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>541</v>
+        <v>505</v>
       </c>
       <c r="B54" t="s">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="E54" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="F54" s="2" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G54" t="s">
-        <v>536</v>
+        <v>500</v>
       </c>
       <c r="H54" t="s">
-        <v>511</v>
+        <v>475</v>
       </c>
       <c r="I54" t="s">
-        <v>542</v>
+        <v>506</v>
       </c>
       <c r="J54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K54" t="s">
-        <v>227</v>
-      </c>
-      <c r="S54" t="s">
-        <v>387</v>
+        <v>216</v>
+      </c>
+      <c r="S54" s="6">
+        <v>44957</v>
       </c>
       <c r="T54" t="s">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="U54" s="4" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="X54" s="4"/>
       <c r="Y54" s="4" t="s">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="Z54" s="4" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/data/proyectos/centroDeProyectos_PMO_2026.xlsx
+++ b/data/proyectos/centroDeProyectos_PMO_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Informe_Interactivo/data/proyectos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42D845F1-3D8F-402A-BDF9-EDE2B85E367C}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F7D8C8D-07ED-46AA-B69E-C9E6CC565515}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
